--- a/Economic modelling/Water Sector.xlsx
+++ b/Economic modelling/Water Sector.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seiorg-my.sharepoint.com/personal/marlon_passos_sei_org/Documents/Documents/KTH PhD/Thesis Work/Task 2/Codes/Economic/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seiorg-my.sharepoint.com/personal/marlon_passos_sei_org/Documents/Documents/KTH PhD/Thesis Work/Task 2/Codes/Github/hydroclimatic-hazards-impacts/Economic modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{8888FB89-D17E-45A1-B1C8-5C1F641564E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1622432-153F-4182-98EC-12F87B5F70BA}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{8888FB89-D17E-45A1-B1C8-5C1F641564E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{815BC39C-C0CB-4681-BE34-CB0A3FDB6BBD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{17957FEF-B149-4C4E-9F98-A1CC7963CF9D}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
   <si>
     <t>Water withdrawal, 1000 cubic meters by type of water and every fifth year</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>*this estimation has been updated to not consider seawater withdrawals, since they are not part of the freshwater supply system</t>
   </si>
 </sst>
 </file>
@@ -1076,22 +1079,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1188D42B-7572-42F6-9E06-0E8F57D49DA6}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>43</v>
       </c>
       <c r="E1" s="1">
-        <f>F9/F12</f>
-        <v>0.65212277000305696</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <f>F9/F7</f>
+        <v>0.8011097477199679</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1100,13 +1106,13 @@
         <v>9.9398950321755941E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
         <v>45</v>
@@ -1124,7 +1130,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
@@ -1145,7 +1151,7 @@
         <v>2573648</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
@@ -1166,7 +1172,7 @@
         <v>314263.25</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>4</v>
       </c>
@@ -1187,7 +1193,7 @@
         <v>2061774.5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>5</v>
       </c>
@@ -1208,7 +1214,7 @@
         <v>587987.5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>197610.5</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
@@ -1249,20 +1255,22 @@
         <f t="shared" si="0"/>
         <v>3161635.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
